--- a/Bangalore-January-2026.xlsx
+++ b/Bangalore-January-2026.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="75">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="76">
   <si>
     <t>Sr. No</t>
   </si>
@@ -94,6 +94,9 @@
     <t>Profit %</t>
   </si>
   <si>
+    <t>Unnamed: 26</t>
+  </si>
+  <si>
     <t>Bangalore</t>
   </si>
   <si>
@@ -181,22 +184,22 @@
     <t>BALENO</t>
   </si>
   <si>
-    <t>Celerio</t>
-  </si>
-  <si>
-    <t>Crysta</t>
+    <t>CELERIO</t>
+  </si>
+  <si>
+    <t>CRYSTA</t>
   </si>
   <si>
     <t>DZIRE</t>
   </si>
   <si>
-    <t>Fortuner</t>
+    <t>FORTUNER</t>
   </si>
   <si>
     <t>HYCROSS</t>
   </si>
   <si>
-    <t>MG EVS</t>
+    <t>MG ZS EV</t>
   </si>
   <si>
     <t>SWIFT</t>
@@ -600,10 +603,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z27"/>
+  <dimension ref="A1:AA27"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1" spans="1:26">
+    <row r="1" spans="1:27">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -682,25 +685,28 @@
       <c r="Z1" s="1" t="s">
         <v>25</v>
       </c>
+      <c r="AA1" s="1" t="s">
+        <v>26</v>
+      </c>
     </row>
-    <row r="2" spans="1:26">
+    <row r="2" spans="1:27">
       <c r="A2">
         <v>22</v>
       </c>
       <c r="B2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C2" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>2026</v>
       </c>
       <c r="E2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F2" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="G2" s="2">
         <v>45235</v>
@@ -763,24 +769,24 @@
         <v>8</v>
       </c>
     </row>
-    <row r="3" spans="1:26">
+    <row r="3" spans="1:27">
       <c r="A3">
         <v>23</v>
       </c>
       <c r="B3" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C3" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D3">
         <v>2026</v>
       </c>
       <c r="E3" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="F3" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="G3" s="2">
         <v>45174</v>
@@ -843,24 +849,24 @@
         <v>45.2</v>
       </c>
     </row>
-    <row r="4" spans="1:26">
+    <row r="4" spans="1:27">
       <c r="A4">
         <v>24</v>
       </c>
       <c r="B4" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D4">
         <v>2026</v>
       </c>
       <c r="E4" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F4" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G4" s="2">
         <v>43560</v>
@@ -923,27 +929,27 @@
         <v>40.28</v>
       </c>
     </row>
-    <row r="5" spans="1:26">
+    <row r="5" spans="1:27">
       <c r="A5">
         <v>25</v>
       </c>
       <c r="B5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D5">
         <v>2026</v>
       </c>
       <c r="E5" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="F5" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G5" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="H5">
         <v>182959</v>
@@ -1003,27 +1009,27 @@
         <v>54.09</v>
       </c>
     </row>
-    <row r="6" spans="1:26">
+    <row r="6" spans="1:27">
       <c r="A6">
         <v>26</v>
       </c>
       <c r="B6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6">
         <v>2026</v>
       </c>
       <c r="E6" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G6" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="H6">
         <v>131788</v>
@@ -1083,27 +1089,27 @@
         <v>-4.56</v>
       </c>
     </row>
-    <row r="7" spans="1:26">
+    <row r="7" spans="1:27">
       <c r="A7">
         <v>27</v>
       </c>
       <c r="B7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7">
         <v>2026</v>
       </c>
       <c r="E7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="F7" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G7" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="H7">
         <v>92054</v>
@@ -1163,24 +1169,24 @@
         <v>45.78</v>
       </c>
     </row>
-    <row r="8" spans="1:26">
+    <row r="8" spans="1:27">
       <c r="A8">
         <v>28</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8">
         <v>2026</v>
       </c>
       <c r="E8" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="F8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G8" s="2">
         <v>44387</v>
@@ -1243,27 +1249,27 @@
         <v>54.06</v>
       </c>
     </row>
-    <row r="9" spans="1:26">
+    <row r="9" spans="1:27">
       <c r="A9">
         <v>29</v>
       </c>
       <c r="B9" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D9">
         <v>2026</v>
       </c>
       <c r="E9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G9" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="H9">
         <v>86460</v>
@@ -1323,24 +1329,24 @@
         <v>50.11</v>
       </c>
     </row>
-    <row r="10" spans="1:26">
+    <row r="10" spans="1:27">
       <c r="A10">
         <v>30</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D10">
         <v>2026</v>
       </c>
       <c r="E10" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="F10" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G10" s="2">
         <v>44257</v>
@@ -1403,24 +1409,24 @@
         <v>39.09</v>
       </c>
     </row>
-    <row r="11" spans="1:26">
+    <row r="11" spans="1:27">
       <c r="A11">
         <v>31</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D11">
         <v>2026</v>
       </c>
       <c r="E11" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G11" s="2">
         <v>44387</v>
@@ -1483,24 +1489,24 @@
         <v>54.71</v>
       </c>
     </row>
-    <row r="12" spans="1:26">
+    <row r="12" spans="1:27">
       <c r="A12">
         <v>32</v>
       </c>
       <c r="B12" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D12">
         <v>2026</v>
       </c>
       <c r="E12" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F12" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G12" s="2">
         <v>45147</v>
@@ -1563,24 +1569,24 @@
         <v>-23.18</v>
       </c>
     </row>
-    <row r="13" spans="1:26">
+    <row r="13" spans="1:27">
       <c r="A13">
         <v>33</v>
       </c>
       <c r="B13" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D13">
         <v>2026</v>
       </c>
       <c r="E13" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G13" s="2">
         <v>44746</v>
@@ -1643,27 +1649,27 @@
         <v>62.66</v>
       </c>
     </row>
-    <row r="14" spans="1:26">
+    <row r="14" spans="1:27">
       <c r="A14">
         <v>34</v>
       </c>
       <c r="B14" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D14">
         <v>2026</v>
       </c>
       <c r="E14" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G14" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="H14">
         <v>69136</v>
@@ -1723,27 +1729,27 @@
         <v>60.48</v>
       </c>
     </row>
-    <row r="15" spans="1:26">
+    <row r="15" spans="1:27">
       <c r="A15">
         <v>35</v>
       </c>
       <c r="B15" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D15">
         <v>2026</v>
       </c>
       <c r="E15" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="F15" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="H15">
         <v>67398</v>
@@ -1803,24 +1809,24 @@
         <v>83.45</v>
       </c>
     </row>
-    <row r="16" spans="1:26">
+    <row r="16" spans="1:27">
       <c r="A16">
         <v>36</v>
       </c>
       <c r="B16" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D16">
         <v>2026</v>
       </c>
       <c r="E16" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F16" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G16" s="2">
         <v>44629</v>
@@ -1888,22 +1894,22 @@
         <v>37</v>
       </c>
       <c r="B17" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D17">
         <v>2026</v>
       </c>
       <c r="E17" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F17" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G17" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="H17">
         <v>66868</v>
@@ -1968,22 +1974,22 @@
         <v>38</v>
       </c>
       <c r="B18" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D18">
         <v>2026</v>
       </c>
       <c r="E18" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F18" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="G18" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="H18">
         <v>12259</v>
@@ -2048,19 +2054,19 @@
         <v>39</v>
       </c>
       <c r="B19" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D19">
         <v>2026</v>
       </c>
       <c r="E19" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="F19" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G19" s="2">
         <v>45174</v>
@@ -2128,22 +2134,22 @@
         <v>40</v>
       </c>
       <c r="B20" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C20" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D20">
         <v>2026</v>
       </c>
       <c r="E20" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="F20" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G20" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H20">
         <v>66912</v>
@@ -2208,22 +2214,22 @@
         <v>41</v>
       </c>
       <c r="B21" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C21" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D21">
         <v>2026</v>
       </c>
       <c r="E21" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="F21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="G21" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="H21">
         <v>82372</v>
@@ -2288,22 +2294,22 @@
         <v>42</v>
       </c>
       <c r="B22" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C22" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D22">
         <v>2026</v>
       </c>
       <c r="E22" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="F22" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="G22" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="H22">
         <v>46262</v>
@@ -2368,22 +2374,22 @@
         <v>43</v>
       </c>
       <c r="B23" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C23" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D23">
         <v>2026</v>
       </c>
       <c r="E23" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F23" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G23" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="H23">
         <v>116342</v>
@@ -2448,22 +2454,22 @@
         <v>44</v>
       </c>
       <c r="B24" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C24" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D24">
         <v>2026</v>
       </c>
       <c r="E24" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="F24" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G24" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H24">
         <v>132185</v>
@@ -2528,22 +2534,22 @@
         <v>45</v>
       </c>
       <c r="B25" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C25" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D25">
         <v>2026</v>
       </c>
       <c r="E25" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="F25" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="G25" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="H25">
         <v>139298</v>
@@ -2608,22 +2614,22 @@
         <v>46</v>
       </c>
       <c r="B26" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C26" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D26">
         <v>2026</v>
       </c>
       <c r="E26" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="F26" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="G26" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="H26">
         <v>44418</v>
@@ -2688,19 +2694,19 @@
         <v>47</v>
       </c>
       <c r="B27" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C27" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D27">
         <v>2026</v>
       </c>
       <c r="E27" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="F27" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="G27" s="2">
         <v>45174</v>
